--- a/evaluation/PERTANYAAN_DOKUMEN_with_candidate.xlsx
+++ b/evaluation/PERTANYAAN_DOKUMEN_with_candidate.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Anak usia 5-14 tahun menderita anemia dengan presentase 26,4%.</t>
+          <t>prevalensi anemia pada perempuan usia ≥15 tahun sebesar 22,7%</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Anak usia 15-24 tahun menderita anemia dengan presentase 18,4%.</t>
+          <t>anak usia 5-14 tahun menderita anemia 26,4% dan usia</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Anemia merupakan salah satu masalah kesehatan masyarakat di Indonesia yang dapat dialami oleh semua kelompok umur mulai dari balita, remaja, ibu hamil sampai usia lanjut.</t>
+          <t>BUKU SAKU PENCEGAHAN ANEMIA PADA IBU HAMIL DAN REMAJA PUTRI</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sumber utama vitamin A adalah minyak ikan dan hati sapi. Sumber lain adalah hati.</t>
+          <t>Vitamin A: Sumber utama vitamin A adalah minyak ikan dan hati sapi.</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sumber utama vitamin E adalah minyak sayur seperti minyak kelapa, minyak kelapa sawit, dan minyak kacang.</t>
+          <t>Vitamin E: Minyak sayur seperti minyak kelapa, minyak kelapa sawit, dan minyak kacang</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Maaf, saya tidak tahu karena informasi tersebut tidak ada di dokumen.</t>
+          <t>BUKU SAKU PENCEGAHAN ANEMIA PADA IBU HAMIL DAN REMAJA PUTRI</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Prevalensi anemia pada usia 5-14 tahun adalah 26,8%.</t>
+          <t>prevalensi anemia pada perempuan usia ≥15 tahun sebesar 22,7%</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Prevalensi anemia pada usia 15-24 tahun adalah 32%.</t>
+          <t>prevalensi anemia pada perempuan usia ≥15 tahun sebesar 22,7%</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Salah satu target prioritas nasional dalam RPJMN 2020-2024 adalah penurunan stunting menjadi 14% pada tahun 2024 melalui implementasi intervensi gizi spesifik maupun intervensi gizi sensitif.</t>
+          <t>putri (Rematri) merupakan salah satu pelayanan gizi</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>TTD tidak berbahaya dan aman dikonsumsi secara rutin, namun konsumsi secara terus menerus perlu mendapat perhatian pada sekelompok populasi yang mempunyai penyakit darah seperti thalassemia, hemosiderosis.</t>
+          <t>Namun, konsumsi TTD secara terus menerus perlu</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Prevalensi anemia pada WUS usia 15 tahun ke atas sebesar 22,7%.</t>
+          <t>prevalensi anemia pada perempuan usia ≥15 tahun sebesar 22,7%</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Prevalensi anemia pada ibu hamil sebesar 37,1%.</t>
+          <t>sedangkan prevalensi anemia pada ibu hamil sebesar 37,1%.</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Tujuan umum program penanggulangan anemia pada remaja dan wanita usia subur (WUS) adalah menurunkan prevalensi anemia pada remaja dan WUS.</t>
+          <t>anemia pada rematri dan WUS adalah cakupan program anemia pada</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Prevalensi anemia pada remaja (usia 10-19 tahun) sebesar 30%.</t>
+          <t>55 BUKU SAKU PENCEGAHAN ANEMIA PADA IBU HAMIL DAN REMAJA PUTRI Lampiran 4. Contoh menu dalam 1 kali Makan Kemenkes RI 26 BUKU SAKU PENCEGAHAN ANEMIA PADA IBU HAMIL DAN REMAJA PUTRI B.</t>
         </is>
       </c>
     </row>
@@ -776,13 +776,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Risiko penderita anemia ketika menjadi ibu hamil adalah:
-- Pertumbuhan dan perkembangan janin yang tidak optimal
-- Komplikasi kehamilan dan persalinan
-- Kematian ibu dan anak
-- Meningkatnya risiko persalinan
-- Kematian ibu dan bayi
-- Infeksi penyakit.</t>
+          <t>BUKU SAKU PENCEGAHAN ANEMIA PADA IBU HAMIL DAN REMAJA PUTRI</t>
         </is>
       </c>
     </row>

--- a/evaluation/PERTANYAAN_DOKUMEN_with_candidate.xlsx
+++ b/evaluation/PERTANYAAN_DOKUMEN_with_candidate.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>prevalensi anemia pada perempuan usia ≥15 tahun sebesar 22,7%</t>
+          <t>Berdasarkan Riskesdas 2013, anak usia 5-14 tahun menderita anemia 26,4% dan usia 15-24 tahun sebesar 18,4%.</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>anak usia 5-14 tahun menderita anemia 26,4% dan usia</t>
+          <t>Berdasarkan Riskesdas 2013, anak usia 5-14 tahun menderita anemia 26,4% dan usia 15-24 tahun sebesar 18,4%.</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>BUKU SAKU PENCEGAHAN ANEMIA PADA IBU HAMIL DAN REMAJA PUTRI</t>
+          <t>Anemia adalah suatu kondisi tubuh dimana kadar hemoglobin (Hb) dalam sel darah merah lebih rendah dari standar yang seharusnya.</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Vitamin A: Sumber utama vitamin A adalah minyak ikan dan hati sapi.</t>
+          <t>Kekurangan asupan zat gizi (zat besi, asam folat, vitamin B12, dan protein) sehingga mengganggu pembentukan hemoglobin; • Rata-rata pola konsumsi masyarakat Indonesia berisiko menderita anemia, terutama anemia defisiensi/ kekurangan besi karena kurang asupan pangan sumber zat besi.</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Vitamin E: Minyak sayur seperti minyak kelapa, minyak kelapa sawit, dan minyak kacang</t>
+          <t>Kekurangan asupan zat gizi (zat besi, asam folat, vitamin B12, dan protein) sehingga mengganggu pembentukan hemoglobin; • Rata-rata pola konsumsi masyarakat Indonesia berisiko menderita anemia, terutama anemia defisiensi/ kekurangan besi karena kurang asupan pangan sumber zat besi.</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>BUKU SAKU PENCEGAHAN ANEMIA PADA IBU HAMIL DAN REMAJA PUTRI</t>
+          <t>Suplementasi TTD pada Rematri merupakan salah satu upaya pemerintah untuk memenuhi asupan zat besi untuk mencegah anemia yang dapat menyebabkan: • Menurunnnya daya tahan tubuh sehingga mudah terkena penyakit infeksi • Menurunnya kebugaran dan ketangkasan berpikir karena kurangnya orksigen ke sel otot dan sel otak • Menurunnya prestasi belajar • Dalam jangka panjang jika rematri tersebut menjadi ibu hamil maka akan menjadi ibu hamil yang anemia juga yang akan meningkatkan risiko persalinan, kematian ibu dan bayi, serta infeksi penyakit.</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>prevalensi anemia pada perempuan usia ≥15 tahun sebesar 22,7%</t>
+          <t>Berdasarkan Riskesdas 2018, prevalensi anemia pada ibu hamil 48,9%, dan prevalensi anemia pada usia 5-14 tahun (26,8%) dan usia 15-24 tahun (32%).</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>prevalensi anemia pada perempuan usia ≥15 tahun sebesar 22,7%</t>
+          <t>Berdasarkan Riskesdas 2018, prevalensi anemia pada ibu hamil 48,9%, dan prevalensi anemia pada usia 5-14 tahun (26,8%) dan usia 15-24 tahun (32%).</t>
         </is>
       </c>
     </row>
@@ -644,7 +644,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>putri (Rematri) merupakan salah satu pelayanan gizi</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Namun, konsumsi TTD secara terus menerus perlu</t>
+          <t>Tablet Tambah Darah (TTD) Bahaya Jika Dikonsumsi secara Terus Menerus/Rutin TTD tidak berbahaya dan aman dikonsumsi oleh ibu hamil dan remaja putri secara rutin karena: • Tubuh akan secara otomatis menyerap zat besi yang dikonsumsi jika tubuh kekurangan zat besi.</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>prevalensi anemia pada perempuan usia ≥15 tahun sebesar 22,7%</t>
+          <t>Anemia : Suatu kondisi tubuh yang ditandai dengan hasil pemeriksaan kadar hemoglobin (Hb) dalam darah lebih rendah dari normal TTD : Suplemen gizi dengan kandungan zat besi setara 60 mg besi elemental dan 400 mcg asam folat Berat Badan Lahir rendah : Bayi baru lahir dengan berat badan kurang dari Bayi Premature Bayi yang lahir pada usia kehamilan kurang dari 37 minggu Stunting : Kondisi gagal tumbuh dan kembang pada anak berusia di bawah lima tahun (balita) akibat asupan gizi yang kurang dalam waktu yang lama, penyakit infeksi berulang, dan stimulasi psikososial yang tidak memadai, ditandai dengan panjang atau tinggi badannya berada di bawah standar (PB/U atau TB/U &lt;-2 SD) (WHO Gizi Spesifik : Upaya dan kegiatan yang langsung mengatasi terjadinya stunting seperti asupan makanan, infeksi, status gizi ibu, penyakit menular, dan kesehatan lingkungan.</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>sedangkan prevalensi anemia pada ibu hamil sebesar 37,1%.</t>
+          <t>Salah satu upaya yang harus dilakukan untuk menurunkan stunting adalah dengan menurunkan prevalensi anemia pada ibu hamil dan pada remaja putri agar bila kelak menikah dan hamil tidak anemia.</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>anemia pada rematri dan WUS adalah cakupan program anemia pada</t>
+          <t>Buku Saku Pencegahan Anemia pada Ibu Hamil dan Remaja Putri merupakan media informasi untuk meningkatkan pengetahuan tenaga kesehatan, kader termasuk kader kesehatan sekolah, guru, pendamping keluarga serta stakeholder terkait.</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>55 BUKU SAKU PENCEGAHAN ANEMIA PADA IBU HAMIL DAN REMAJA PUTRI Lampiran 4. Contoh menu dalam 1 kali Makan Kemenkes RI 26 BUKU SAKU PENCEGAHAN ANEMIA PADA IBU HAMIL DAN REMAJA PUTRI B.</t>
+          <t>Anemia : Suatu kondisi tubuh yang ditandai dengan hasil pemeriksaan kadar hemoglobin (Hb) dalam darah lebih rendah dari normal TTD : Suplemen gizi dengan kandungan zat besi setara 60 mg besi elemental dan 400 mcg asam folat Berat Badan Lahir rendah : Bayi baru lahir dengan berat badan kurang dari Bayi Premature Bayi yang lahir pada usia kehamilan kurang dari 37 minggu Stunting : Kondisi gagal tumbuh dan kembang pada anak berusia di bawah lima tahun (balita) akibat asupan gizi yang kurang dalam waktu yang lama, penyakit infeksi berulang, dan stimulasi psikososial yang tidak memadai, ditandai dengan panjang atau tinggi badannya berada di bawah standar (PB/U atau TB/U &lt;-2 SD) (WHO Gizi Spesifik : Upaya dan kegiatan yang langsung mengatasi terjadinya stunting seperti asupan makanan, infeksi, status gizi ibu, penyakit menular, dan kesehatan lingkungan.</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>BUKU SAKU PENCEGAHAN ANEMIA PADA IBU HAMIL DAN REMAJA PUTRI</t>
+          <t>Suplementasi TTD pada Rematri merupakan salah satu upaya pemerintah untuk memenuhi asupan zat besi untuk mencegah anemia yang dapat menyebabkan: • Menurunnnya daya tahan tubuh sehingga mudah terkena penyakit infeksi • Menurunnya kebugaran dan ketangkasan berpikir karena kurangnya orksigen ke sel otot dan sel otak • Menurunnya prestasi belajar • Dalam jangka panjang jika rematri tersebut menjadi ibu hamil maka akan menjadi ibu hamil yang anemia juga yang akan meningkatkan risiko persalinan, kematian ibu dan bayi, serta infeksi penyakit.</t>
         </is>
       </c>
     </row>

--- a/evaluation/PERTANYAAN_DOKUMEN_with_candidate.xlsx
+++ b/evaluation/PERTANYAAN_DOKUMEN_with_candidate.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,6 +449,11 @@
           <t>Candidate</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Candidate_Raw</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -468,6 +473,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Berdasarkan hasil penelusuran dokumen, anak usia 5-14 tahun menderita anemia 26,4%</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>Berdasarkan Riskesdas 2013, anak usia 5-14 tahun menderita anemia 26,4% dan usia 15-24 tahun sebesar 18,4%.</t>
         </is>
       </c>
@@ -490,6 +500,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>Berdasarkan hasil penelusuran dokumen, anak usia 15-24 tahun menderita anemia 16,4%</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>Berdasarkan Riskesdas 2013, anak usia 5-14 tahun menderita anemia 26,4% dan usia 15-24 tahun sebesar 18,4%.</t>
         </is>
       </c>
@@ -515,6 +530,11 @@
           <t>Anemia adalah suatu kondisi tubuh dimana kadar hemoglobin (Hb) dalam sel darah merah lebih rendah dari standar yang seharusnya.</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Anemia adalah suatu kondisi tubuh dimana kadar hemoglobin (Hb) dalam sel darah merah lebih rendah dari standar yang seharusnya.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -534,7 +554,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Kekurangan asupan zat gizi (zat besi, asam folat, vitamin B12, dan protein) sehingga mengganggu pembentukan hemoglobin; • Rata-rata pola konsumsi masyarakat Indonesia berisiko menderita anemia, terutama anemia defisiensi/ kekurangan besi karena kurang asupan pangan sumber zat besi.</t>
+          <t>Berdasarkan hasil penelusuran dokumen, Sumber utama vitamin A adalah minyak ikan dan hati sapi</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Makanan sumber zat besi seperti: 1) Sumber makanan yang kaya besi adalah pangan hewani karena mengandung zat besi (besi heme) yang mudah diserap dalam pencernaan.</t>
         </is>
       </c>
     </row>
@@ -556,6 +581,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>Berdasarkan hasil penelusuran dokumen, Minyak sayur seperti minyak kelapa, minyak kelapa sawit, dan minyak kacang kedelai.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>Kekurangan asupan zat gizi (zat besi, asam folat, vitamin B12, dan protein) sehingga mengganggu pembentukan hemoglobin; • Rata-rata pola konsumsi masyarakat Indonesia berisiko menderita anemia, terutama anemia defisiensi/ kekurangan besi karena kurang asupan pangan sumber zat besi.</t>
         </is>
       </c>
@@ -578,7 +608,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Suplementasi TTD pada Rematri merupakan salah satu upaya pemerintah untuk memenuhi asupan zat besi untuk mencegah anemia yang dapat menyebabkan: • Menurunnnya daya tahan tubuh sehingga mudah terkena penyakit infeksi • Menurunnya kebugaran dan ketangkasan berpikir karena kurangnya orksigen ke sel otot dan sel otak • Menurunnya prestasi belajar • Dalam jangka panjang jika rematri tersebut menjadi ibu hamil maka akan menjadi ibu hamil yang anemia juga yang akan meningkatkan risiko persalinan, kematian ibu dan bayi, serta infeksi penyakit.</t>
+          <t>Berdasarkan hasil penelusuran dokumen, Prevalensi anemia pada ibu hamil di Indonesia adalah 48,9% berdasarkan Riskesdas 2018</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Berdasarkan Riskesdas 2018, prevalensi anemia pada ibu hamil 48,9%, dan prevalensi anemia pada usia 5-14 tahun (26,8%) dan usia 15-24 tahun (32%).</t>
         </is>
       </c>
     </row>
@@ -600,6 +635,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>Berdasarkan hasil penelusuran dokumen, Prevalensi anemia pada usia 5-14 tahun adalah 26,8% menurut Riskesdas 2018</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>Berdasarkan Riskesdas 2018, prevalensi anemia pada ibu hamil 48,9%, dan prevalensi anemia pada usia 5-14 tahun (26,8%) dan usia 15-24 tahun (32%).</t>
         </is>
       </c>
@@ -622,6 +662,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>Berdasarkan hasil penelusuran dokumen, Prevalensi anemia pada usia 15-24 tahun adalah 32% berdasarkan Riskesdas 2018</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>Berdasarkan Riskesdas 2018, prevalensi anemia pada ibu hamil 48,9%, dan prevalensi anemia pada usia 5-14 tahun (26,8%) dan usia 15-24 tahun (32%).</t>
         </is>
       </c>
@@ -644,6 +689,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>Berdasarkan hasil penelusuran dokumen, Salah satu target prioritas nasional dalam RPJMN 2020-2024 adalah menurunkan stunting menjadi 14% pada tahun 2024.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>UNKNOWN</t>
         </is>
       </c>
@@ -666,6 +716,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>Berdasarkan hasil penelusuran dokumen, TTD tidak berbahaya dan aman dikonsumsi oleh ibu hamil dan remaja putri secara rutin karena Tubuh akan secara otomatis menyerap zat besi yang dikonsumsi jika tubuh kekurangan zat besi.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>Tablet Tambah Darah (TTD) Bahaya Jika Dikonsumsi secara Terus Menerus/Rutin TTD tidak berbahaya dan aman dikonsumsi oleh ibu hamil dan remaja putri secara rutin karena: • Tubuh akan secara otomatis menyerap zat besi yang dikonsumsi jika tubuh kekurangan zat besi.</t>
         </is>
       </c>
@@ -688,7 +743,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Anemia : Suatu kondisi tubuh yang ditandai dengan hasil pemeriksaan kadar hemoglobin (Hb) dalam darah lebih rendah dari normal TTD : Suplemen gizi dengan kandungan zat besi setara 60 mg besi elemental dan 400 mcg asam folat Berat Badan Lahir rendah : Bayi baru lahir dengan berat badan kurang dari Bayi Premature Bayi yang lahir pada usia kehamilan kurang dari 37 minggu Stunting : Kondisi gagal tumbuh dan kembang pada anak berusia di bawah lima tahun (balita) akibat asupan gizi yang kurang dalam waktu yang lama, penyakit infeksi berulang, dan stimulasi psikososial yang tidak memadai, ditandai dengan panjang atau tinggi badannya berada di bawah standar (PB/U atau TB/U &lt;-2 SD) (WHO Gizi Spesifik : Upaya dan kegiatan yang langsung mengatasi terjadinya stunting seperti asupan makanan, infeksi, status gizi ibu, penyakit menular, dan kesehatan lingkungan.</t>
+          <t>Berdasarkan hasil penelusuran dokumen, prevalensi anemia pada WUS usia 15 tahun ke atas sebesar 22,7%,</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Berdasarkan Riskesdas 2018, prevalensi anemia pada ibu hamil 48,9%, dan prevalensi anemia pada usia 5-14 tahun (26,8%) dan usia 15-24 tahun (32%).</t>
         </is>
       </c>
     </row>
@@ -710,7 +770,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Salah satu upaya yang harus dilakukan untuk menurunkan stunting adalah dengan menurunkan prevalensi anemia pada ibu hamil dan pada remaja putri agar bila kelak menikah dan hamil tidak anemia.</t>
+          <t>Berdasarkan hasil penelusuran dokumen, pada ibu hamil sebesar 37.1%</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Berdasarkan Riskesdas 2018, prevalensi anemia pada ibu hamil 48,9%, dan prevalensi anemia pada usia 5-14 tahun (26,8%) dan usia 15-24 tahun (32%).</t>
         </is>
       </c>
     </row>
@@ -732,7 +797,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Buku Saku Pencegahan Anemia pada Ibu Hamil dan Remaja Putri merupakan media informasi untuk meningkatkan pengetahuan tenaga kesehatan, kader termasuk kader kesehatan sekolah, guru, pendamping keluarga serta stakeholder terkait.</t>
+          <t>Berdasarkan hasil penelusuran dokumen, Menurunkan prevalensi anemia pada remaja dan WUS</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Pemberian TTD untuk WUS Lainnya yang Tidak Hamil Wanita Usia Subur adalah wanita yang masih dalam rentang usia reproduktif yaitu antara usia 15-49 tahun, baik yang sedang hamil maupun tidak, termasuk calon pengantin (catin).</t>
         </is>
       </c>
     </row>
@@ -754,7 +824,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Anemia : Suatu kondisi tubuh yang ditandai dengan hasil pemeriksaan kadar hemoglobin (Hb) dalam darah lebih rendah dari normal TTD : Suplemen gizi dengan kandungan zat besi setara 60 mg besi elemental dan 400 mcg asam folat Berat Badan Lahir rendah : Bayi baru lahir dengan berat badan kurang dari Bayi Premature Bayi yang lahir pada usia kehamilan kurang dari 37 minggu Stunting : Kondisi gagal tumbuh dan kembang pada anak berusia di bawah lima tahun (balita) akibat asupan gizi yang kurang dalam waktu yang lama, penyakit infeksi berulang, dan stimulasi psikososial yang tidak memadai, ditandai dengan panjang atau tinggi badannya berada di bawah standar (PB/U atau TB/U &lt;-2 SD) (WHO Gizi Spesifik : Upaya dan kegiatan yang langsung mengatasi terjadinya stunting seperti asupan makanan, infeksi, status gizi ibu, penyakit menular, dan kesehatan lingkungan.</t>
+          <t>Berdasarkan hasil penelusuran dokumen, Data SKRT tahun 2001 menunjukkan bahwa prevalensi anemia pada remaja (usia 10-19 tahun) sebesar 30%.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Berdasarkan Riskesdas 2018, prevalensi anemia pada ibu hamil 48,9%, dan prevalensi anemia pada usia 5-14 tahun (26,8%) dan usia 15-24 tahun (32%).</t>
         </is>
       </c>
     </row>
@@ -776,7 +851,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Suplementasi TTD pada Rematri merupakan salah satu upaya pemerintah untuk memenuhi asupan zat besi untuk mencegah anemia yang dapat menyebabkan: • Menurunnnya daya tahan tubuh sehingga mudah terkena penyakit infeksi • Menurunnya kebugaran dan ketangkasan berpikir karena kurangnya orksigen ke sel otot dan sel otak • Menurunnya prestasi belajar • Dalam jangka panjang jika rematri tersebut menjadi ibu hamil maka akan menjadi ibu hamil yang anemia juga yang akan meningkatkan risiko persalinan, kematian ibu dan bayi, serta infeksi penyakit.</t>
+          <t>Berdasarkan hasil penelusuran dokumen, rematri yang menderita anemia ketika menjadi ibu hamil berisiko melahirkan berat bayi lahir rendah dan stunting</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Berdasarkan Riskesdas 2018, prevalensi anemia pada ibu hamil 48,9%, dan prevalensi anemia pada usia 5-14 tahun (26,8%) dan usia 15-24 tahun (32%).</t>
         </is>
       </c>
     </row>
